--- a/resources/templates/standard/D1100-04.xlsx
+++ b/resources/templates/standard/D1100-04.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -664,7 +667,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -705,15 +710,15 @@
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
       <c r="AO1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ1" s="4"/>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -818,7 +823,7 @@
     </row>
     <row r="4" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -863,7 +868,7 @@
       <c r="AP4" s="7"/>
       <c r="AQ4" s="7"/>
       <c r="AR4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS4" s="4"/>
       <c r="AT4" s="4"/>
@@ -878,62 +883,62 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
       <c r="T5" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X5" s="9"/>
       <c r="Y5" s="9"/>
       <c r="Z5" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA5" s="9"/>
       <c r="AB5" s="9"/>
       <c r="AC5" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD5" s="9"/>
       <c r="AE5" s="9"/>
       <c r="AF5" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG5" s="9"/>
       <c r="AH5" s="9"/>
       <c r="AI5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9"/>
       <c r="AL5" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
       <c r="AO5" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP5" s="9"/>
       <c r="AQ5" s="9"/>
@@ -944,7 +949,7 @@
     </row>
     <row r="6" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -995,7 +1000,7 @@
     </row>
     <row r="7" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1046,7 +1051,7 @@
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -1097,7 +1102,7 @@
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -1148,7 +1153,7 @@
     </row>
     <row r="10" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -1199,7 +1204,7 @@
     </row>
     <row r="11" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
